--- a/Team-Data/2007-08/2-21-2007-08.xlsx
+++ b/Team-Data/2007-08/2-21-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -972,10 +1039,10 @@
         <v>20</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -1154,13 +1221,13 @@
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV4" t="n">
         <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1339,7 +1406,7 @@
         <v>19</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW5" t="n">
         <v>12</v>
@@ -1351,7 +1418,7 @@
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
         <v>14</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1555,7 @@
         <v>9</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1719,7 @@
         <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="n">
         <v>7</v>
@@ -1664,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ7" t="n">
         <v>26</v>
@@ -1679,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF8" t="n">
         <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>7</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
         <v>10</v>
@@ -1897,7 +1964,7 @@
         <v>20</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2119,7 @@
         <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
@@ -2070,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2265,7 @@
         <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF10" t="n">
         <v>11</v>
@@ -2237,7 +2304,7 @@
         <v>18</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -2299,49 +2366,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.63</v>
+        <v>0.623</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J11" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L11" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O11" t="n">
         <v>16.6</v>
       </c>
       <c r="P11" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q11" t="n">
         <v>0.729</v>
       </c>
       <c r="R11" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S11" t="n">
         <v>32.1</v>
@@ -2350,16 +2417,16 @@
         <v>44.2</v>
       </c>
       <c r="U11" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="V11" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y11" t="n">
         <v>4.4</v>
@@ -2371,16 +2438,16 @@
         <v>20.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>96</v>
+        <v>95.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF11" t="n">
         <v>9</v>
@@ -2389,10 +2456,10 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ11" t="n">
         <v>13</v>
@@ -2410,7 +2477,7 @@
         <v>22</v>
       </c>
       <c r="AO11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP11" t="n">
         <v>24</v>
@@ -2419,7 +2486,7 @@
         <v>22</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
         <v>7</v>
@@ -2428,7 +2495,7 @@
         <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV11" t="n">
         <v>13</v>
@@ -2446,13 +2513,13 @@
         <v>4</v>
       </c>
       <c r="BA11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
         <v>19</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -2574,13 +2641,13 @@
         <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ12" t="n">
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
         <v>4</v>
@@ -2616,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -2762,10 +2829,10 @@
         <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
         <v>27</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3226,7 @@
         <v>24</v>
       </c>
       <c r="AV15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
         <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>0.17</v>
+        <v>0.173</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3239,55 +3306,55 @@
         <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="O16" t="n">
         <v>18</v>
       </c>
       <c r="P16" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.716</v>
+        <v>0.718</v>
       </c>
       <c r="R16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="T16" t="n">
         <v>38.3</v>
       </c>
       <c r="U16" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X16" t="n">
         <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA16" t="n">
         <v>21.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.7</v>
+        <v>-7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3317,10 +3384,10 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP16" t="n">
         <v>16</v>
@@ -3332,16 +3399,16 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
       </c>
       <c r="AU16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW16" t="n">
         <v>18</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -3496,10 +3563,10 @@
         <v>22</v>
       </c>
       <c r="AM17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN17" t="n">
         <v>21</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>23</v>
       </c>
       <c r="AO17" t="n">
         <v>25</v>
@@ -3529,7 +3596,7 @@
         <v>22</v>
       </c>
       <c r="AX17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
         <v>21</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -3573,43 +3640,43 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
         <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>0.208</v>
+        <v>0.212</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J18" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="L18" t="n">
         <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="O18" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P18" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.724</v>
@@ -3618,16 +3685,16 @@
         <v>12.3</v>
       </c>
       <c r="S18" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T18" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U18" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="V18" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W18" t="n">
         <v>7.5</v>
@@ -3639,19 +3706,19 @@
         <v>5.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AA18" t="n">
         <v>17.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.2</v>
+        <v>-7.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3672,16 +3739,16 @@
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
       </c>
       <c r="AM18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3699,7 +3766,7 @@
         <v>19</v>
       </c>
       <c r="AT18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
         <v>27</v>
@@ -3708,7 +3775,7 @@
         <v>23</v>
       </c>
       <c r="AW18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3930,7 @@
         <v>19</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>3</v>
@@ -4075,7 +4142,7 @@
         <v>9</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY20" t="n">
         <v>11</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4294,7 @@
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
         <v>13</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ21" t="n">
         <v>18</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4494,7 @@
         <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
         <v>23</v>
@@ -4454,7 +4521,7 @@
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4661,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP23" t="n">
         <v>13</v>
@@ -4606,13 +4673,13 @@
         <v>2</v>
       </c>
       <c r="AS23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4843,7 @@
         <v>3</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
         <v>25</v>
@@ -4809,7 +4876,7 @@
         <v>2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F25" t="n">
         <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>0.537</v>
+        <v>0.528</v>
       </c>
       <c r="H25" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I25" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="J25" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L25" t="n">
         <v>6.4</v>
@@ -4880,22 +4947,22 @@
         <v>0.378</v>
       </c>
       <c r="O25" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="P25" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.758</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S25" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="T25" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U25" t="n">
         <v>21.4</v>
@@ -4904,10 +4971,10 @@
         <v>13.2</v>
       </c>
       <c r="W25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="X25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y25" t="n">
         <v>3.8</v>
@@ -4916,19 +4983,19 @@
         <v>19.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4958,19 +5025,19 @@
         <v>6</v>
       </c>
       <c r="AO25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>27</v>
@@ -4985,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY25" t="n">
         <v>3</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5119,7 +5186,7 @@
         <v>16</v>
       </c>
       <c r="AH26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI26" t="n">
         <v>19</v>
@@ -5152,7 +5219,7 @@
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT26" t="n">
         <v>28</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
         <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J27" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0.458</v>
@@ -5238,19 +5305,19 @@
         <v>7.9</v>
       </c>
       <c r="M27" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O27" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P27" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R27" t="n">
         <v>9.800000000000001</v>
@@ -5271,7 +5338,7 @@
         <v>6.5</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
         <v>4.5</v>
@@ -5286,10 +5353,10 @@
         <v>96.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>6</v>
@@ -5301,10 +5368,10 @@
         <v>6</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>27</v>
@@ -5322,13 +5389,13 @@
         <v>5</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP27" t="n">
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR27" t="n">
         <v>24</v>
@@ -5340,7 +5407,7 @@
         <v>19</v>
       </c>
       <c r="AU27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV27" t="n">
         <v>5</v>
@@ -5349,7 +5416,7 @@
         <v>23</v>
       </c>
       <c r="AX27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E28" t="n">
         <v>14</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G28" t="n">
-        <v>0.264</v>
+        <v>0.269</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J28" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L28" t="n">
         <v>4.3</v>
@@ -5423,61 +5490,61 @@
         <v>12.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O28" t="n">
         <v>17.5</v>
       </c>
       <c r="P28" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.764</v>
+        <v>0.767</v>
       </c>
       <c r="R28" t="n">
         <v>11.8</v>
       </c>
       <c r="S28" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T28" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="U28" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V28" t="n">
         <v>16</v>
       </c>
       <c r="W28" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="n">
         <v>20</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="AC28" t="n">
-        <v>-6.9</v>
+        <v>-7</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
       </c>
       <c r="AF28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG28" t="n">
         <v>27</v>
@@ -5486,7 +5553,7 @@
         <v>16</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ28" t="n">
         <v>3</v>
@@ -5495,16 +5562,16 @@
         <v>23</v>
       </c>
       <c r="AL28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM28" t="n">
         <v>26</v>
       </c>
       <c r="AN28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
         <v>23</v>
@@ -5534,10 +5601,10 @@
         <v>6</v>
       </c>
       <c r="AY28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
         <v>25</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>4.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5686,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP29" t="n">
         <v>29</v>
@@ -5713,7 +5780,7 @@
         <v>21</v>
       </c>
       <c r="AX29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY29" t="n">
         <v>6</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF30" t="n">
         <v>7</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6032,7 +6099,7 @@
         <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
@@ -6062,7 +6129,7 @@
         <v>4</v>
       </c>
       <c r="AS31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT31" t="n">
         <v>11</v>
@@ -6080,13 +6147,13 @@
         <v>16</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>6</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-21-2007-08</t>
+          <t>2008-02-21</t>
         </is>
       </c>
     </row>
